--- a/entorno/mir-v2/plantillas/LEGAJO_NYA_2026_T1_MODELO.xlsx
+++ b/entorno/mir-v2/plantillas/LEGAJO_NYA_2026_T1_MODELO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="NyA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NyA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/plantillas/LEGAJO_NYA_2026_T1_MODELO.xlsx
+++ b/entorno/mir-v2/plantillas/LEGAJO_NYA_2026_T1_MODELO.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NyA" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prov_Dto_Localidad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="NyA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Prov_Dto_Localidad" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,10 +35,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -102,10 +97,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -185,182 +176,171 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>ID del Niño, niña o Adolescente
-Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.
-Qué se espera: un número entero
-Campo obligatorio.</t>
+        <t>ID del niño, niña o adolescente
+Obligatorio
+Qué va: Número entero.
+Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
       <text>
         <t>Apellido/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
         <t>Nombre/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
         <t>Tipo de documento de identidad
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "Tipo de documento de identidad".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: DNI, Documento extranjero, Otro tipo de documentación, Sin documentación.</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
         <t>Nº DNI
-Qué se espera: texto
-Máximo 15 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 15 caracteres.
+No se puede repetir en la hoja.</t>
       </text>
     </comment>
     <comment ref="F2" authorId="0" shapeId="0">
       <text>
         <t>Nº de CUIL
-Qué se espera: texto
-Máximo 13 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 13 caracteres.
+Tiene que ser un CUIL válido: se controla el dígito verificador.
+Aviso: Con el formato NN-NNNNNNNN-N.</t>
       </text>
     </comment>
     <comment ref="G2" authorId="0" shapeId="0">
       <text>
         <t>Otro núero de documentación de identidad (si no cuenta con DNI)
-Qué se espera: texto
-Máximo 15 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 15 caracteres.
+No se puede repetir en la hoja.</t>
       </text>
     </comment>
     <comment ref="H2" authorId="0" shapeId="0">
       <text>
         <t>Género
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Género".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Masculino, Femenino, Otros.</t>
       </text>
     </comment>
     <comment ref="I2" authorId="0" shapeId="0">
       <text>
         <t>País de nacimiento
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "País de nacimiento (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 11 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
         <t>Fecha de nacimiento
-Qué se espera: una fecha, con formato dd/mm/aaaa
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
         <t>Domicilio actual
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
         <t>Provincia
-Qué se espera: texto
-Máximo 120 caracteres.
-Elegir de la lista "Provincia (nomenclador oficial)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.</t>
       </text>
     </comment>
     <comment ref="M2" authorId="0" shapeId="0">
       <text>
         <t>Departamento
-Qué se espera: texto
-Elegir de la lista "Departamento (nomenclador oficial)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="N2" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-Elegir de la lista "Localidad (lista de la jurisdicción)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.</t>
       </text>
     </comment>
     <comment ref="O2" authorId="0" shapeId="0">
       <text>
         <t>¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="P2" authorId="0" shapeId="0">
       <text>
         <t>Pueblo originario (especificar)
-Qué se espera: texto
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto.
+Obligatorio si «¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)» es «Sí».</t>
       </text>
     </comment>
     <comment ref="Q2" authorId="0" shapeId="0">
       <text>
         <t>¿Presenta algún tipo de discapacidad?
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Discapacidad (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No presenta discapacidad, Visual, Auditiva, Mental, Motora, Visceral, Otros, Sin dato.</t>
       </text>
     </comment>
     <comment ref="R2" authorId="0" shapeId="0">
       <text>
         <t>¿Posee CUD?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Posee CUD?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, En trámite, Vencido, No aplica, Sin datos.</t>
       </text>
     </comment>
     <comment ref="S2" authorId="0" shapeId="0">
       <text>
         <t>Cobertura salud
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "Cobertura salud (legajo)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Pública exclusivamente, Obra Social, Prepaga, Otra cobertura, Sin datos.</t>
       </text>
     </comment>
     <comment ref="T2" authorId="0" shapeId="0">
       <text>
         <t>¿Tiene hijos/as?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="U2" authorId="0" shapeId="0">
       <text>
         <t>Fecha de actualización
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
   </commentList>
@@ -370,31 +350,28 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>PROVINCIA
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>DEPTO
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>LOCALIDAD
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
   </commentList>
@@ -719,7 +696,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente *</t>
+          <t>ID del niño, niña o adolescente *</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -1826,28 +1803,28 @@
   </sheetData>
   <dataValidations count="8">
     <dataValidation sqref="D3:D202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de documento de identidad&quot;." type="list">
-      <formula1>LISTAS!$J$2:$J$5</formula1>
+      <formula1>Listas!$J$2:$J$5</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Género&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$4</formula1>
+      <formula1>Listas!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;País de nacimiento&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$12</formula1>
+      <formula1>Listas!$G$2:$G$12</formula1>
     </dataValidation>
     <dataValidation sqref="O3:O202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)&quot;." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>Listas!$I$2:$I$4</formula1>
     </dataValidation>
     <dataValidation sqref="Q3:Q202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Presenta algún tipo de discapacidad?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$9</formula1>
+      <formula1>Listas!$B$2:$B$9</formula1>
     </dataValidation>
     <dataValidation sqref="R3:R202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Posee CUD?&quot;." type="list">
-      <formula1>LISTAS!$H$2:$H$7</formula1>
+      <formula1>Listas!$H$2:$H$7</formula1>
     </dataValidation>
     <dataValidation sqref="S3:S202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cobertura salud&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="T3:T202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Tiene hijos/as?&quot;." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>Listas!$I$2:$I$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1899,320 +1876,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: NyA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Identificador que le asigna el sistema provincial al niño, niña o adolescente. Es la clave con la que las nóminas (MPE, MPI, MPJ) se enganchan a este legajo.
-Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Apellido/s</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Nombre/s</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tipo de documento de identidad</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Tipo de documento de identidad".</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Nº DNI</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Nº de CUIL</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Otro núero de documentación de identidad (si no cuenta con DNI)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Género".</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>País de nacimiento</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "País de nacimiento (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fecha de nacimiento</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Domicilio actual</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Provincia (nomenclador oficial)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Departamento</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Departamento (nomenclador oficial)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Localidad (lista de la jurisdicción)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>¿Pertenece a pueblo originario? (o se identifica con algún pueblo originario?)</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Pueblo originario (especificar)</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>¿Presenta algún tipo de discapacidad?</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Discapacidad (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>¿Posee CUD?</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Posee CUD?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cobertura salud</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cobertura salud (legajo)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>¿Tiene hijos/as?</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fecha de actualización</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: Prov_Dto_Localidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>DEPTO</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LOCALIDAD</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
